--- a/SHCourseGroupCodeAdmin/Template/修課檢核課程代碼樣板.xlsx
+++ b/SHCourseGroupCodeAdmin/Template/修課檢核課程代碼樣板.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ischoolProject\ScoreReportDAL\SHCourseGroupCodeAdmin\Template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C06F7233-E3B3-465D-A91A-455E287618FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E9B704A-D632-42EF-9725-8BE1EA9AC3C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,8 +16,12 @@
     <sheet name="檢查修課學生課程代碼" sheetId="1" r:id="rId1"/>
     <sheet name="檢查修課學生課程代碼(有差異)" sheetId="2" r:id="rId2"/>
     <sheet name="檢查學生應修課程代碼未修" sheetId="3" r:id="rId3"/>
+    <sheet name="檢查修課學生課程代碼_統計" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="152511"/>
+  <pivotCaches>
+    <pivotCache cacheId="0" r:id="rId5"/>
+  </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -873,7 +877,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="31">
   <si>
     <t>學號</t>
   </si>
@@ -953,13 +957,36 @@
   </si>
   <si>
     <t>報部科目名稱</t>
+  </si>
+  <si>
+    <t>加總 - 學分數</t>
+  </si>
+  <si>
+    <t>欄標籤</t>
+  </si>
+  <si>
+    <t>總計</t>
+  </si>
+  <si>
+    <t>列標籤</t>
+  </si>
+  <si>
+    <t>(空白)</t>
+  </si>
+  <si>
+    <t>修課課程代碼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>與課規課程代碼有差異</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -996,6 +1023,13 @@
       <family val="3"/>
       <charset val="136"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1014,21 +1048,40 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
+    <cellStyle name="一般 2" xfId="1" xr:uid="{3A7D8857-6060-4DD2-9D49-5F1A3ED82436}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1041,6 +1094,220 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="ChunTai Chen" refreshedDate="46055.017284027781" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="1" xr:uid="{80432198-2AB9-421D-B849-3DCA2B17F94B}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:T1048576" sheet="檢查修課學生課程代碼"/>
+  </cacheSource>
+  <cacheFields count="20">
+    <cacheField name="學年度" numFmtId="0">
+      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
+    </cacheField>
+    <cacheField name="學期" numFmtId="0">
+      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
+    </cacheField>
+    <cacheField name="年級" numFmtId="0">
+      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
+    </cacheField>
+    <cacheField name="學號" numFmtId="0">
+      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
+    </cacheField>
+    <cacheField name="班級" numFmtId="0">
+      <sharedItems containsNonDate="0" containsString="0" containsBlank="1" count="1">
+        <m/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="座號" numFmtId="0">
+      <sharedItems containsNonDate="0" containsString="0" containsBlank="1" count="1">
+        <m/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="姓名" numFmtId="0">
+      <sharedItems containsNonDate="0" containsString="0" containsBlank="1" count="1">
+        <m/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="課程名稱" numFmtId="0">
+      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
+    </cacheField>
+    <cacheField name="科目名稱" numFmtId="0">
+      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
+    </cacheField>
+    <cacheField name="科目級別" numFmtId="0">
+      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
+    </cacheField>
+    <cacheField name="部定校訂" numFmtId="0">
+      <sharedItems containsNonDate="0" containsString="0" containsBlank="1" count="1">
+        <m/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="必修選修" numFmtId="0">
+      <sharedItems containsNonDate="0" containsString="0" containsBlank="1" count="1">
+        <m/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="分項類別" numFmtId="0">
+      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
+    </cacheField>
+    <cacheField name="學分數" numFmtId="0">
+      <sharedItems containsNonDate="0" containsString="0" containsBlank="1" count="1">
+        <m/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="節數" numFmtId="0">
+      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
+    </cacheField>
+    <cacheField name="課程代碼" numFmtId="0">
+      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
+    </cacheField>
+    <cacheField name="授課學期學分節數" numFmtId="0">
+      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
+    </cacheField>
+    <cacheField name="開課方式" numFmtId="0">
+      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
+    </cacheField>
+    <cacheField name="課程規劃表" numFmtId="0">
+      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
+    </cacheField>
+    <cacheField name="報部科目名稱" numFmtId="0">
+      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="1">
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <x v="0"/>
+    <m/>
+    <x v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FD99B830-5CEF-4C47-9289-E9D11F5E8665}" name="樞紐分析表1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:C9" firstHeaderRow="1" firstDataRow="3" firstDataCol="1"/>
+  <pivotFields count="20">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" defaultSubtotal="0">
+      <items count="1">
+        <item x="0"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" showAll="0" defaultSubtotal="0">
+      <items count="1">
+        <item x="0"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="3">
+    <field x="4"/>
+    <field x="5"/>
+    <field x="6"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="2">
+      <x/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="2">
+    <field x="10"/>
+    <field x="11"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+      <x/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="加總 - 學分數" fld="13" baseField="4" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1306,7 +1573,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T1"/>
+  <dimension ref="A1:U1"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="5.5" bestFit="1" customWidth="1"/>
@@ -1317,7 +1584,7 @@
     <col min="20" max="20" width="13.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>18</v>
       </c>
@@ -1364,7 +1631,7 @@
         <v>10</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="Q1" s="1" t="s">
         <v>12</v>
@@ -1377,6 +1644,9 @@
       </c>
       <c r="T1" t="s">
         <v>23</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1539,4 +1809,72 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D394029-DC66-4F29-B3B8-0FE8C0678218}">
+  <dimension ref="A3:C9"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="6" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/SHCourseGroupCodeAdmin/Template/修課檢核課程代碼樣板.xlsx
+++ b/SHCourseGroupCodeAdmin/Template/修課檢核課程代碼樣板.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ischoolProject\ScoreReportDAL\SHCourseGroupCodeAdmin\Template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E9B704A-D632-42EF-9725-8BE1EA9AC3C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F93E8827-62AC-494F-8CAA-13F9B131BAC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,9 +18,12 @@
     <sheet name="檢查學生應修課程代碼未修" sheetId="3" r:id="rId3"/>
     <sheet name="檢查修課學生課程代碼_統計" sheetId="5" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName name="ptSrc_CheckSCAttendCourseCode">檢查修課學生課程代碼!$A$1:$U$2</definedName>
+  </definedNames>
   <calcPr calcId="152511"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId5"/>
+    <pivotCache cacheId="7" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -1097,11 +1100,11 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="ChunTai Chen" refreshedDate="46055.017284027781" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="1" xr:uid="{80432198-2AB9-421D-B849-3DCA2B17F94B}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="ChunTai Chen" refreshedDate="46085.481579976855" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="1" xr:uid="{A050EB8B-FB14-4580-B028-F6A20740F6D4}">
   <cacheSource type="worksheet">
-    <worksheetSource ref="A1:T1048576" sheet="檢查修課學生課程代碼"/>
+    <worksheetSource name="ptSrc_CheckSCAttendCourseCode"/>
   </cacheSource>
-  <cacheFields count="20">
+  <cacheFields count="21">
     <cacheField name="學年度" numFmtId="0">
       <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
     </cacheField>
@@ -1152,14 +1155,12 @@
       <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
     </cacheField>
     <cacheField name="學分數" numFmtId="0">
-      <sharedItems containsNonDate="0" containsString="0" containsBlank="1" count="1">
-        <m/>
-      </sharedItems>
+      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
     </cacheField>
     <cacheField name="節數" numFmtId="0">
       <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
     </cacheField>
-    <cacheField name="課程代碼" numFmtId="0">
+    <cacheField name="修課課程代碼" numFmtId="0">
       <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
     </cacheField>
     <cacheField name="授課學期學分節數" numFmtId="0">
@@ -1172,6 +1173,9 @@
       <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
     </cacheField>
     <cacheField name="報部科目名稱" numFmtId="0">
+      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
+    </cacheField>
+    <cacheField name="與課規課程代碼有差異" numFmtId="0">
       <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
     </cacheField>
   </cacheFields>
@@ -1199,7 +1203,8 @@
     <x v="0"/>
     <x v="0"/>
     <m/>
-    <x v="0"/>
+    <m/>
+    <m/>
     <m/>
     <m/>
     <m/>
@@ -1211,9 +1216,9 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FD99B830-5CEF-4C47-9289-E9D11F5E8665}" name="樞紐分析表1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A108E1DC-5730-429C-A13B-9F09AD2EC09C}" name="樞紐分析表1" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:C9" firstHeaderRow="1" firstDataRow="3" firstDataCol="1"/>
-  <pivotFields count="20">
+  <pivotFields count="21">
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -1250,12 +1255,8 @@
       </items>
     </pivotField>
     <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0">
-      <items count="2">
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
